--- a/artfynd/A 46146-2024 artfynd.xlsx
+++ b/artfynd/A 46146-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>120854809</v>
       </c>
       <c r="B3" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120854797</v>
+        <v>120854788</v>
       </c>
       <c r="B4" t="n">
-        <v>57717</v>
+        <v>57367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,20 +896,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -920,7 +920,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768987</v>
+        <v>768941</v>
       </c>
       <c r="R4" t="n">
-        <v>7084230</v>
+        <v>7084254</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,6 +975,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -991,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120854812</v>
+        <v>120854797</v>
       </c>
       <c r="B5" t="n">
-        <v>78598</v>
+        <v>57720</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,38 +1023,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768887</v>
+        <v>768987</v>
       </c>
       <c r="R5" t="n">
-        <v>7084351</v>
+        <v>7084230</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120854785</v>
+        <v>120854783</v>
       </c>
       <c r="B6" t="n">
-        <v>57364</v>
+        <v>90662</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1130,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768991</v>
+        <v>768939</v>
       </c>
       <c r="R6" t="n">
-        <v>7084200</v>
+        <v>7084406</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,11 +1196,6 @@
           <t>2024-11-02</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Silverfura, högstubbe med gamla spillkråkehack</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1187,22 +1207,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Silverfura</t>
+          <t>Granlåga, tunnare i mossa</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Silverfura</t>
+          <t>Picea abies # Granlåga, tunnare i mossa</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1220,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120854790</v>
+        <v>120854785</v>
       </c>
       <c r="B7" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,21 +1274,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>768891</v>
+        <v>768991</v>
       </c>
       <c r="R7" t="n">
-        <v>7084344</v>
+        <v>7084200</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1320,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Födosök i myrstack, gjort sommar/höst troligen</t>
+          <t>Silverfura, högstubbe med gamla spillkråkehack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,6 +1331,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Silverfura</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Silverfura</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1332,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120854810</v>
+        <v>120854812</v>
       </c>
       <c r="B8" t="n">
-        <v>90705</v>
+        <v>78601</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>768960</v>
+        <v>768887</v>
       </c>
       <c r="R8" t="n">
-        <v>7084401</v>
+        <v>7084351</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,26 +1453,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Granlåga, knäckt</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga, knäckt</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1454,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120854788</v>
+        <v>120854790</v>
       </c>
       <c r="B9" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>768941</v>
+        <v>768891</v>
       </c>
       <c r="R9" t="n">
-        <v>7084254</v>
+        <v>7084344</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,6 +1552,11 @@
           <t>2024-11-02</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Födosök i myrstack, gjort sommar/höst troligen</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1545,26 +1565,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120854783</v>
+        <v>120854810</v>
       </c>
       <c r="B10" t="n">
-        <v>90652</v>
+        <v>90715</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,25 +1593,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>768939</v>
+        <v>768960</v>
       </c>
       <c r="R10" t="n">
-        <v>7084406</v>
+        <v>7084401</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,12 +1680,12 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>Granlåga, tunnare i mossa</t>
+          <t>Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, tunnare i mossa</t>
+          <t>Picea abies # Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 46146-2024 artfynd.xlsx
+++ b/artfynd/A 46146-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120854809</v>
+        <v>120854812</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,43 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>768943</v>
+        <v>768887</v>
       </c>
       <c r="R3" t="n">
-        <v>7084424</v>
+        <v>7084351</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120854788</v>
+        <v>120854809</v>
       </c>
       <c r="B4" t="n">
-        <v>57367</v>
+        <v>57372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,31 +891,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100110</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768941</v>
+        <v>768943</v>
       </c>
       <c r="R4" t="n">
-        <v>7084254</v>
+        <v>7084424</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,26 +970,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1011,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120854797</v>
+        <v>120854810</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>90715</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,43 +998,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768987</v>
+        <v>768960</v>
       </c>
       <c r="R5" t="n">
-        <v>7084230</v>
+        <v>7084401</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,6 +1072,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Granlåga, knäckt</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga, knäckt</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1118,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120854783</v>
+        <v>120854785</v>
       </c>
       <c r="B6" t="n">
-        <v>90662</v>
+        <v>57367</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,25 +1120,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768939</v>
+        <v>768991</v>
       </c>
       <c r="R6" t="n">
-        <v>7084406</v>
+        <v>7084200</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,6 +1186,11 @@
           <t>2024-11-02</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Silverfura, högstubbe med gamla spillkråkehack</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1207,22 +1202,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Granlåga, tunnare i mossa</t>
+          <t>Silverfura</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, tunnare i mossa</t>
+          <t>Pinus sylvestris # Silverfura</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1240,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120854785</v>
+        <v>120854788</v>
       </c>
       <c r="B7" t="n">
         <v>57367</v>
@@ -1274,16 +1269,21 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>768991</v>
+        <v>768941</v>
       </c>
       <c r="R7" t="n">
-        <v>7084200</v>
+        <v>7084254</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,11 +1318,6 @@
           <t>2024-11-02</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Silverfura, högstubbe med gamla spillkråkehack</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1334,22 +1329,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Silverfura</t>
+          <t>Granhögstubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Silverfura</t>
+          <t>Picea abies # Granhögstubbe</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1367,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120854812</v>
+        <v>120854797</v>
       </c>
       <c r="B8" t="n">
-        <v>78601</v>
+        <v>57720</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,38 +1374,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>768887</v>
+        <v>768987</v>
       </c>
       <c r="R8" t="n">
-        <v>7084351</v>
+        <v>7084230</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120854790</v>
+        <v>120854783</v>
       </c>
       <c r="B9" t="n">
-        <v>57367</v>
+        <v>90662</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,43 +1481,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>768891</v>
+        <v>768939</v>
       </c>
       <c r="R9" t="n">
-        <v>7084344</v>
+        <v>7084406</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,11 +1547,6 @@
           <t>2024-11-02</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Födosök i myrstack, gjort sommar/höst troligen</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1565,6 +1555,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Granlåga, tunnare i mossa</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga, tunnare i mossa</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1581,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120854810</v>
+        <v>120854790</v>
       </c>
       <c r="B10" t="n">
-        <v>90715</v>
+        <v>57367</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,34 +1607,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>768960</v>
+        <v>768891</v>
       </c>
       <c r="R10" t="n">
-        <v>7084401</v>
+        <v>7084344</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,6 +1674,11 @@
           <t>2024-11-02</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födosök i myrstack, gjort sommar/höst troligen</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1667,26 +1687,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>Granlåga, knäckt</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga, knäckt</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">

--- a/artfynd/A 46146-2024 artfynd.xlsx
+++ b/artfynd/A 46146-2024 artfynd.xlsx
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123622687</v>
+        <v>123622686</v>
       </c>
       <c r="B11" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768885</v>
+        <v>768894</v>
       </c>
       <c r="R11" t="n">
-        <v>7084358</v>
+        <v>7084354</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1815,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123622686</v>
+        <v>123622687</v>
       </c>
       <c r="B12" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>768894</v>
+        <v>768885</v>
       </c>
       <c r="R12" t="n">
-        <v>7084354</v>
+        <v>7084358</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1930,7 +1930,7 @@
         <v>123622683</v>
       </c>
       <c r="B13" t="n">
-        <v>57851</v>
+        <v>57857</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 46146-2024 artfynd.xlsx
+++ b/artfynd/A 46146-2024 artfynd.xlsx
@@ -1706,7 +1706,7 @@
         <v>123622686</v>
       </c>
       <c r="B11" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>123622687</v>
       </c>
       <c r="B12" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>123622683</v>
       </c>
       <c r="B13" t="n">
-        <v>57857</v>
+        <v>57860</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 46146-2024 artfynd.xlsx
+++ b/artfynd/A 46146-2024 artfynd.xlsx
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123622686</v>
+        <v>123622683</v>
       </c>
       <c r="B11" t="n">
-        <v>78786</v>
+        <v>57861</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,41 +1715,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>O Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768894</v>
+        <v>768922</v>
       </c>
       <c r="R11" t="n">
-        <v>7084354</v>
+        <v>7084452</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1818,7 +1827,7 @@
         <v>123622687</v>
       </c>
       <c r="B12" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1927,10 +1936,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123622683</v>
+        <v>123622686</v>
       </c>
       <c r="B13" t="n">
-        <v>57860</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1939,50 +1948,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>O Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>768922</v>
+        <v>768894</v>
       </c>
       <c r="R13" t="n">
-        <v>7084452</v>
+        <v>7084354</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 46146-2024 artfynd.xlsx
+++ b/artfynd/A 46146-2024 artfynd.xlsx
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123622683</v>
+        <v>123622687</v>
       </c>
       <c r="B11" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,50 +1715,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>O Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768922</v>
+        <v>768885</v>
       </c>
       <c r="R11" t="n">
-        <v>7084452</v>
+        <v>7084358</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1824,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123622687</v>
+        <v>123622683</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,41 +1827,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>O Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>768885</v>
+        <v>768922</v>
       </c>
       <c r="R12" t="n">
-        <v>7084358</v>
+        <v>7084452</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 46146-2024 artfynd.xlsx
+++ b/artfynd/A 46146-2024 artfynd.xlsx
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123622687</v>
+        <v>123622683</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,41 +1715,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>O Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768885</v>
+        <v>768922</v>
       </c>
       <c r="R11" t="n">
-        <v>7084358</v>
+        <v>7084452</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1815,10 +1824,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123622683</v>
+        <v>123622686</v>
       </c>
       <c r="B12" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,50 +1836,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>O Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>768922</v>
+        <v>768894</v>
       </c>
       <c r="R12" t="n">
-        <v>7084452</v>
+        <v>7084354</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123622686</v>
+        <v>123622687</v>
       </c>
       <c r="B13" t="n">
         <v>78788</v>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>768894</v>
+        <v>768885</v>
       </c>
       <c r="R13" t="n">
-        <v>7084354</v>
+        <v>7084358</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 46146-2024 artfynd.xlsx
+++ b/artfynd/A 46146-2024 artfynd.xlsx
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123622683</v>
+        <v>123622686</v>
       </c>
       <c r="B11" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,50 +1715,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>O Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768922</v>
+        <v>768894</v>
       </c>
       <c r="R11" t="n">
-        <v>7084452</v>
+        <v>7084354</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1824,7 +1815,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123622686</v>
+        <v>123622687</v>
       </c>
       <c r="B12" t="n">
         <v>78788</v>
@@ -1864,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>768894</v>
+        <v>768885</v>
       </c>
       <c r="R12" t="n">
-        <v>7084354</v>
+        <v>7084358</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1936,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123622687</v>
+        <v>123622683</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,41 +1939,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>O Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>768885</v>
+        <v>768922</v>
       </c>
       <c r="R13" t="n">
-        <v>7084358</v>
+        <v>7084452</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 46146-2024 artfynd.xlsx
+++ b/artfynd/A 46146-2024 artfynd.xlsx
@@ -1703,7 +1703,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123622686</v>
+        <v>123622687</v>
       </c>
       <c r="B11" t="n">
         <v>78788</v>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768894</v>
+        <v>768885</v>
       </c>
       <c r="R11" t="n">
-        <v>7084354</v>
+        <v>7084358</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1815,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123622687</v>
+        <v>123622683</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,41 +1827,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>O Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>768885</v>
+        <v>768922</v>
       </c>
       <c r="R12" t="n">
-        <v>7084358</v>
+        <v>7084452</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1927,10 +1936,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123622683</v>
+        <v>123622686</v>
       </c>
       <c r="B13" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1939,50 +1948,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>O Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>768922</v>
+        <v>768894</v>
       </c>
       <c r="R13" t="n">
-        <v>7084452</v>
+        <v>7084354</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 46146-2024 artfynd.xlsx
+++ b/artfynd/A 46146-2024 artfynd.xlsx
@@ -1815,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123622683</v>
+        <v>123622686</v>
       </c>
       <c r="B12" t="n">
-        <v>57861</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,50 +1827,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>O Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>768922</v>
+        <v>768894</v>
       </c>
       <c r="R12" t="n">
-        <v>7084452</v>
+        <v>7084354</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1936,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123622686</v>
+        <v>123622683</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>57861</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,41 +1939,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>O Spångmyran, Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>768894</v>
+        <v>768922</v>
       </c>
       <c r="R13" t="n">
-        <v>7084354</v>
+        <v>7084452</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
